--- a/source_data/Tax Complexity Variable Notes.xlsx
+++ b/source_data/Tax Complexity Variable Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\international-tax-competitiveness-index\source_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079C1D57-7080-478F-BDAB-F140924E34D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4717015C-26F2-4CD2-BD3D-B62974CEF3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{799C6252-BD7E-43F6-A84E-AA4474677B14}"/>
   </bookViews>

--- a/source_data/Tax Complexity Variable Notes.xlsx
+++ b/source_data/Tax Complexity Variable Notes.xlsx
@@ -8,17 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\international-tax-competitiveness-index\source_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4717015C-26F2-4CD2-BD3D-B62974CEF3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9D1269-AA21-4D74-BB14-7E7CB87C59FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{799C6252-BD7E-43F6-A84E-AA4474677B14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="VAT" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$489</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">VAT!$A$1:$C$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$490</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -164,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="401">
   <si>
     <t>Australia</t>
   </si>
@@ -1931,65 +1929,6 @@
     <t>EY 2016: Surcharge later ruled unconstitutional</t>
   </si>
   <si>
-    <t>EY 2014: The basic rate of national corporation tax
-is 25.5% for tax years beginning on or after 1 April 2012. For
-corporations capitalized at JPY100 million or less, a tax rate of
-19% applies to the first JPY8 million of taxable income. The tax
-rate of 19% is reduced to 15% for tax years beginning between
-1 April 2012 and 31 March 2015.</t>
-  </si>
-  <si>
-    <t>EY 2015: The basic rate of national corporation tax
-is 25.5% for tax years beginning on or after 1 April 2012. For
-corporations capitalized at JPY100 million or less, a tax rate of
-19% applies to the first JPY8 million of taxable income. The tax
-rate of 19% is reduced to 15% for tax years beginning between
-1 April 2012 and 31 March 2015.</t>
-  </si>
-  <si>
-    <t>EY 2016: The basic rate of national corporation tax
-is 23.9% for fiscal years beginning on or after 1 April 2015. For
-corporations with stated capital of JPY100 million or less, a tax
-rate of 15% applies to the first JPY8 million of taxable income.
-The tax rate of 15% applies for fiscal years beginning between
-1 April 2012 and 31 March 2017.</t>
-  </si>
-  <si>
-    <t>EY 2017: The basic rate of national corporation tax
-is 23.4% for fiscal years beginning on or after 1 April 2016. For
-corporations with stated capital of JPY100 million or less, a tax
-rate of 15% applies to the first JPY8 million of taxable income.
-The tax rate of 15% applies for fiscal years beginning between
-1 April 2012 and 31 March 2017.</t>
-  </si>
-  <si>
-    <t>EY 2018: The basic rate of national corporation tax
-is 23.4% for fiscal years beginning on or after 1 April 2016. For
-corporations with stated capital of JPY100 million or less, a tax
-rate of 15% applies to the first JPY8 million of taxable income.
-The tax rate of 15% applies for fiscal years beginning between
-1 April 2012 and 31 March 2019.</t>
-  </si>
-  <si>
-    <t>EY 2019: The basic rate of national corporation tax
-is 23.2% for fiscal years beginning on or after 1 April 2018. For
-corporations with stated capital of JPY100 million or less, a tax
-rate of 15% applies to the first JPY8 million of taxable income.
-The tax rate of 15% applies for fiscal years beginning between
-1 April 2012 and 31 March 2019.</t>
-  </si>
-  <si>
-    <t>EY 2020: The basic rate of national corporation tax is 23.2% for fiscal years beginning on or after 1 April 2018. For corporations with stated capital of JPY100 million or less, a tax rate of 15% applies to the first JPY8 million of taxable income. The tax rate of 15% applies for fiscal years beginning between 1 April 2012 and 31 March 2021.</t>
-  </si>
-  <si>
-    <t>EY 2021: The basic rate of national corporation tax
-is 23.2% for fiscal years beginning on or after 1 April 2018. For
-corporations with stated capital of JPY100 million or less, a tax
-rate of 15% applies to the first JPY8 million of taxable income.
-The tax rate of 15% applies for fiscal years beginning between
-1 April 2012 and 31 March 2021.</t>
-  </si>
-  <si>
     <t>EY 2018: Domestic corporations. Corporate income tax is imposed at a rate
 of 10% on taxable income up to KRW200 million, at a rate of
 20% on taxable income in excess of KRW200 million up to
@@ -3188,9 +3127,6 @@
     <t>EY 2021: BEAT+GILTI</t>
   </si>
   <si>
-    <t>higher_or_reduced</t>
-  </si>
-  <si>
     <t>vat_reduced_or_higher</t>
   </si>
   <si>
@@ -3258,9 +3194,6 @@
   </si>
   <si>
     <t>EY 2022: Regular rate + IRAP. No policy change.</t>
-  </si>
-  <si>
-    <t>Two CIT brackets. No policy change.</t>
   </si>
   <si>
     <t>No policy changes.</t>
@@ -3330,9 +3263,6 @@
     <t>1) Reduced rate of 20%, 2) Special reduced rate of 9%</t>
   </si>
   <si>
-    <t>Three CIT brackets: 23.2%, 19%, and 15%</t>
-  </si>
-  <si>
     <t>Four CIT brackets and minimum tax. No policy changes.</t>
   </si>
   <si>
@@ -3423,9 +3353,6 @@
     <t>QDMTT + domestic minimum tax</t>
   </si>
   <si>
-    <t>Two CIT brackets: 23.2% and 19%</t>
-  </si>
-  <si>
     <t>FCT rate for the ProPYME (SMEs) Regime is temporarily reduced to 12.5% for fiscal years 2025, 2026, and 2027</t>
   </si>
   <si>
@@ -3442,13 +3369,28 @@
   </si>
   <si>
     <t>2 reduced rates + QMDTT + domestic minimum CIT</t>
+  </si>
+  <si>
+    <t>BEAT+NCTI.</t>
+  </si>
+  <si>
+    <t>National rates 25.5% (general) and 15% (first JPY 8m, capital &lt;= JPY 100m). Distinct combined rates = 9: capital &lt;= JPY 100m at the standard enterprise rate across the three income brackets (&lt;= 4m / 4-8m / &gt; 8m) = 3; the same three brackets at the Tokyo super rate (income &gt; 25m or revenue &gt; 200m) = 3; capital &gt; JPY 100m at the graduated enterprise income base across three brackets = 3. Score = 9 - 1 = 8.</t>
+  </si>
+  <si>
+    <t>No change to structure</t>
+  </si>
+  <si>
+    <t>The FY2022 reform withdrew the graduated income-base enterprise rates for size-based taxpayers, collapsing the three capital &gt; JPY 100m cells to one. Distinct combined rates = 7: capital &lt;= JPY 100m at the standard rate (3 brackets) and the super rate (3 brackets) = 6; capital &gt; JPY 100m at a single flat income-base rate = 1 (graduated brackets withdrawn for size-based taxpayers, FY2022 reform, Local Tax Act art. 72-24-7). Score = 7 - 1 = 6.</t>
+  </si>
+  <si>
+    <t>The 2025 Tax Reform Act extended the 15% band to FY beginning before 1 Apr 2027 and added a 17% band for income above JPY 1bn, restoring the count to nine. Distinct combined rates = 9: capital &lt;= JPY 100m at the standard rate (3 brackets) = 3 and the super rate (3 brackets) = 3; the 17% band for income &gt; JPY 1bn on the first two brackets = 2; capital &gt; JPY 100m flat = 1. Score = 9 - 1 = 8.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3465,12 +3407,6 @@
     <font>
       <sz val="11"/>
       <name val="Lato"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -3923,7 +3859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2DF56A-1A76-4E35-AC1A-4D6FF403CC05}">
-  <dimension ref="A1:L489"/>
+  <dimension ref="A1:L491"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.65"/>
   <cols>
     <col min="1" max="2" width="8.87890625" customWidth="1"/>
@@ -3951,7 +3887,7 @@
         <v>120</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>117</v>
@@ -3972,7 +3908,7 @@
         <v>39</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
@@ -4369,7 +4305,7 @@
         <v>2024</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -4407,7 +4343,7 @@
         <v>2025</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F13" s="3">
         <v>3</v>
@@ -4445,7 +4381,7 @@
         <v>2026</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F14" s="3">
         <v>3</v>
@@ -4863,7 +4799,7 @@
         <v>2024</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="F25" s="8">
         <v>3</v>
@@ -4901,7 +4837,7 @@
         <v>2025</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F26" s="6">
         <v>3</v>
@@ -4939,7 +4875,7 @@
         <v>2026</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F27" s="6">
         <v>3</v>
@@ -5357,7 +5293,7 @@
         <v>2024</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="F38">
         <v>2</v>
@@ -5395,7 +5331,7 @@
         <v>2025</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F39" s="3">
         <v>2</v>
@@ -5433,7 +5369,7 @@
         <v>2026</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F40" s="3">
         <v>2</v>
@@ -5775,7 +5711,7 @@
         <v>2022</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -5813,7 +5749,7 @@
         <v>2023</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -5851,7 +5787,7 @@
         <v>2024</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="F51">
         <v>2</v>
@@ -5889,7 +5825,7 @@
         <v>2025</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F52" s="3">
         <v>2</v>
@@ -5927,7 +5863,7 @@
         <v>2026</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F53" s="3">
         <v>2</v>
@@ -6345,7 +6281,7 @@
         <v>2024</v>
       </c>
       <c r="E64" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -6383,7 +6319,7 @@
         <v>2024</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F65" s="3">
         <v>1</v>
@@ -6421,7 +6357,7 @@
         <v>2024</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F66" s="3">
         <v>1</v>
@@ -6763,7 +6699,7 @@
         <v>2022</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -6801,7 +6737,7 @@
         <v>2023</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -6839,7 +6775,7 @@
         <v>2024</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -6877,7 +6813,7 @@
         <v>2025</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F78" s="3">
         <v>1</v>
@@ -6915,7 +6851,7 @@
         <v>2025</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F79" s="3">
         <v>1</v>
@@ -7219,7 +7155,7 @@
         <v>2021</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F87">
         <v>2</v>
@@ -7257,7 +7193,7 @@
         <v>2022</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -7295,7 +7231,7 @@
         <v>2023</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="F89">
         <v>3</v>
@@ -7333,7 +7269,7 @@
         <v>2024</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="F90">
         <v>3</v>
@@ -7371,7 +7307,7 @@
         <v>2025</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F91" s="3">
         <v>3</v>
@@ -7409,7 +7345,7 @@
         <v>2025</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F92" s="3">
         <v>3</v>
@@ -7730,7 +7666,7 @@
         <v>2022</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="F101">
         <v>5</v>
@@ -7768,7 +7704,7 @@
         <v>2023</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -7806,7 +7742,7 @@
         <v>2024</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="F103">
         <v>5</v>
@@ -7844,7 +7780,7 @@
         <v>2025</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F104" s="3">
         <v>5</v>
@@ -7882,7 +7818,7 @@
         <v>2025</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F105" s="3">
         <v>5</v>
@@ -8300,7 +8236,7 @@
         <v>2024</v>
       </c>
       <c r="E116" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -8338,7 +8274,7 @@
         <v>2025</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F117" s="3">
         <v>1</v>
@@ -8376,7 +8312,7 @@
         <v>2025</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F118" s="3">
         <v>1</v>
@@ -8724,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="H127">
         <v>5.5</v>
@@ -8762,7 +8698,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="H128">
         <v>5.5</v>
@@ -8794,13 +8730,13 @@
         <v>2024</v>
       </c>
       <c r="E129" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F129">
         <v>1</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="H129">
         <v>5.5</v>
@@ -8832,13 +8768,13 @@
         <v>2025</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F130" s="3">
         <v>1</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="H130" s="3">
         <v>5.5</v>
@@ -8870,13 +8806,13 @@
         <v>2025</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F131" s="3">
         <v>1</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="H131" s="3">
         <v>5.5</v>
@@ -9288,7 +9224,7 @@
         <v>2024</v>
       </c>
       <c r="E142" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -9326,7 +9262,7 @@
         <v>2025</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F143" s="3">
         <v>1</v>
@@ -9364,7 +9300,7 @@
         <v>2025</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F144" s="3">
         <v>1</v>
@@ -9706,7 +9642,7 @@
         <v>2022</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -9744,7 +9680,7 @@
         <v>2023</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -9782,7 +9718,7 @@
         <v>2024</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -9820,7 +9756,7 @@
         <v>2025</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="F156" s="3">
         <v>0</v>
@@ -9858,7 +9794,7 @@
         <v>2026</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F157" s="3">
         <v>0</v>
@@ -9896,7 +9832,7 @@
         <v>2014</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="F158">
         <v>3</v>
@@ -9934,7 +9870,7 @@
         <v>2015</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F159">
         <v>3</v>
@@ -9972,7 +9908,7 @@
         <v>2016</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -10010,7 +9946,7 @@
         <v>2017</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -10048,7 +9984,7 @@
         <v>2018</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -10086,7 +10022,7 @@
         <v>2019</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -10124,7 +10060,7 @@
         <v>2020</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -10162,7 +10098,7 @@
         <v>2021</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -10200,7 +10136,7 @@
         <v>2022</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F166" s="8">
         <v>2</v>
@@ -10235,7 +10171,7 @@
         <v>2023</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F167" s="8">
         <v>2</v>
@@ -10270,7 +10206,7 @@
         <v>2024</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F168" s="8">
         <v>3</v>
@@ -10305,7 +10241,7 @@
         <v>2025</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="F169" s="6">
         <v>6</v>
@@ -10340,7 +10276,7 @@
         <v>2026</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F170" s="6">
         <v>6</v>
@@ -10755,7 +10691,7 @@
         <v>2024</v>
       </c>
       <c r="E181" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -10793,7 +10729,7 @@
         <v>2024</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F182" s="3">
         <v>1</v>
@@ -10831,7 +10767,7 @@
         <v>2024</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F183" s="3">
         <v>1</v>
@@ -11173,13 +11109,13 @@
         <v>2022</v>
       </c>
       <c r="E192" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F192">
         <v>1</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="H192">
         <v>3.3</v>
@@ -11211,13 +11147,13 @@
         <v>2023</v>
       </c>
       <c r="E193" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F193">
         <v>1</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="H193">
         <v>3.3</v>
@@ -11249,13 +11185,13 @@
         <v>2024</v>
       </c>
       <c r="E194" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="F194">
         <v>2</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="H194">
         <v>3.3</v>
@@ -11287,13 +11223,13 @@
         <v>2024</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="F195" s="10">
         <v>4</v>
       </c>
       <c r="G195" s="11" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="H195" s="10">
         <v>3.3</v>
@@ -11325,7 +11261,7 @@
         <v>2014</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -11363,7 +11299,7 @@
         <v>2015</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F197">
         <v>2</v>
@@ -11401,7 +11337,7 @@
         <v>2016</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F198">
         <v>1</v>
@@ -11439,7 +11375,7 @@
         <v>2017</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -11477,7 +11413,7 @@
         <v>2018</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F200">
         <v>1</v>
@@ -11515,7 +11451,7 @@
         <v>2019</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -11553,7 +11489,7 @@
         <v>2020</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -11591,7 +11527,7 @@
         <v>2021</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -11629,7 +11565,7 @@
         <v>2022</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F204">
         <v>2</v>
@@ -11664,7 +11600,7 @@
         <v>2023</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F205">
         <v>2</v>
@@ -11699,7 +11635,7 @@
         <v>2024</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="F206">
         <v>3</v>
@@ -11734,7 +11670,7 @@
         <v>2025</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F207" s="3">
         <v>3</v>
@@ -12143,7 +12079,7 @@
         <v>2024</v>
       </c>
       <c r="E218" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F218">
         <v>1</v>
@@ -12178,7 +12114,7 @@
         <v>2024</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F219" s="3">
         <v>1</v>
@@ -12517,7 +12453,7 @@
         <v>2022</v>
       </c>
       <c r="E228" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="F228">
         <v>1</v>
@@ -12555,7 +12491,7 @@
         <v>2023</v>
       </c>
       <c r="E229" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="F229">
         <v>1</v>
@@ -12593,7 +12529,7 @@
         <v>2024</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="F230" s="3">
         <v>2</v>
@@ -12631,7 +12567,7 @@
         <v>2025</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F231" s="3">
         <v>2</v>
@@ -12669,7 +12605,7 @@
         <v>2026</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F232" s="3">
         <v>2</v>
@@ -13011,7 +12947,7 @@
         <v>2022</v>
       </c>
       <c r="E241" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F241">
         <v>1</v>
@@ -13049,7 +12985,7 @@
         <v>2023</v>
       </c>
       <c r="E242" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F242">
         <v>1</v>
@@ -13087,7 +13023,7 @@
         <v>2024</v>
       </c>
       <c r="E243" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="F243">
         <v>2</v>
@@ -13125,7 +13061,7 @@
         <v>2024</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F244" s="3">
         <v>2</v>
@@ -13619,7 +13555,7 @@
         <v>2026</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F257" s="6">
         <v>1</v>
@@ -13961,7 +13897,7 @@
         <v>2022</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F266">
         <v>1</v>
@@ -13999,7 +13935,7 @@
         <v>2023</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F267">
         <v>1</v>
@@ -14037,7 +13973,7 @@
         <v>2024</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F268">
         <v>1</v>
@@ -14075,7 +14011,7 @@
         <v>2025</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="F269" s="3">
         <v>1</v>
@@ -14113,7 +14049,7 @@
         <v>2026</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="F270" s="3">
         <v>1</v>
@@ -14449,7 +14385,7 @@
         <v>2022</v>
       </c>
       <c r="E279" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F279">
         <v>1</v>
@@ -14487,7 +14423,7 @@
         <v>2023</v>
       </c>
       <c r="E280" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -14525,7 +14461,7 @@
         <v>2024</v>
       </c>
       <c r="E281" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F281">
         <v>2</v>
@@ -14563,7 +14499,7 @@
         <v>2025</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F282" s="3">
         <v>2</v>
@@ -14601,7 +14537,7 @@
         <v>2026</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F283" s="3">
         <v>2</v>
@@ -14639,10 +14575,10 @@
         <v>2014</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>247</v>
+        <v>397</v>
       </c>
       <c r="F284">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G284" t="s">
         <v>126</v>
@@ -14677,10 +14613,10 @@
         <v>2015</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>248</v>
+        <v>398</v>
       </c>
       <c r="F285">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G285" t="s">
         <v>126</v>
@@ -14715,10 +14651,10 @@
         <v>2016</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>249</v>
+        <v>398</v>
       </c>
       <c r="F286">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G286" t="s">
         <v>126</v>
@@ -14753,10 +14689,10 @@
         <v>2017</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>250</v>
+        <v>398</v>
       </c>
       <c r="F287">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G287" t="s">
         <v>126</v>
@@ -14791,10 +14727,10 @@
         <v>2018</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>251</v>
+        <v>398</v>
       </c>
       <c r="F288">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G288" t="s">
         <v>126</v>
@@ -14829,10 +14765,10 @@
         <v>2019</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>252</v>
+        <v>398</v>
       </c>
       <c r="F289">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G289" t="s">
         <v>126</v>
@@ -14866,11 +14802,11 @@
       <c r="D290">
         <v>2020</v>
       </c>
-      <c r="E290" t="s">
-        <v>253</v>
+      <c r="E290" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="F290">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G290" t="s">
         <v>126</v>
@@ -14905,10 +14841,10 @@
         <v>2021</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="F291">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G291" t="s">
         <v>126</v>
@@ -14943,10 +14879,10 @@
         <v>2022</v>
       </c>
       <c r="E292" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="F292">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G292" t="s">
         <v>126</v>
@@ -14981,10 +14917,10 @@
         <v>2023</v>
       </c>
       <c r="E293" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G293" t="s">
         <v>126</v>
@@ -15019,10 +14955,10 @@
         <v>2024</v>
       </c>
       <c r="E294" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F294">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G294" t="s">
         <v>126</v>
@@ -15057,10 +14993,10 @@
         <v>2025</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F295" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G295" s="3" t="s">
         <v>126</v>
@@ -15095,10 +15031,10 @@
         <v>2026</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="F296" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G296" s="3" t="s">
         <v>126</v>
@@ -15133,13 +15069,13 @@
         <v>2014</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="F297">
         <v>6</v>
       </c>
       <c r="G297" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -15171,13 +15107,13 @@
         <v>2015</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F298">
         <v>4</v>
       </c>
       <c r="G298" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H298">
         <v>0</v>
@@ -15209,13 +15145,13 @@
         <v>2016</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="F299">
         <v>4</v>
       </c>
       <c r="G299" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H299">
         <v>0</v>
@@ -15247,13 +15183,13 @@
         <v>2017</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F300">
         <v>4</v>
       </c>
       <c r="G300" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H300">
         <v>0</v>
@@ -15285,13 +15221,13 @@
         <v>2018</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F301">
         <v>3</v>
       </c>
       <c r="G301" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -15323,13 +15259,13 @@
         <v>2019</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F302">
         <v>4</v>
       </c>
       <c r="G302" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -15361,13 +15297,13 @@
         <v>2020</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F303">
         <v>4</v>
       </c>
       <c r="G303" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H303">
         <v>0</v>
@@ -15399,13 +15335,13 @@
         <v>2021</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="F304">
         <v>4</v>
       </c>
       <c r="G304" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H304" s="5">
         <v>0</v>
@@ -15437,13 +15373,13 @@
         <v>2022</v>
       </c>
       <c r="E305" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="F305">
         <v>4</v>
       </c>
       <c r="G305" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H305" s="5">
         <v>0</v>
@@ -15475,13 +15411,13 @@
         <v>2023</v>
       </c>
       <c r="E306" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="F306">
         <v>4</v>
       </c>
       <c r="G306" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H306" s="5">
         <v>0</v>
@@ -15513,13 +15449,13 @@
         <v>2024</v>
       </c>
       <c r="E307" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="F307">
         <v>4</v>
       </c>
       <c r="G307" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H307" s="5">
         <v>0</v>
@@ -15551,13 +15487,13 @@
         <v>2025</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F308" s="3">
         <v>4</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H308" s="3">
         <v>0</v>
@@ -15589,13 +15525,13 @@
         <v>2026</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F309" s="3">
         <v>5</v>
       </c>
       <c r="G309" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H309" s="3">
         <v>0</v>
@@ -15627,7 +15563,7 @@
         <v>2014</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="F310">
         <v>2</v>
@@ -15665,7 +15601,7 @@
         <v>2015</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="F311">
         <v>2</v>
@@ -15703,7 +15639,7 @@
         <v>2016</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="F312">
         <v>2</v>
@@ -15741,7 +15677,7 @@
         <v>2017</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F313">
         <v>2</v>
@@ -15779,7 +15715,7 @@
         <v>2018</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F314">
         <v>2</v>
@@ -15817,7 +15753,7 @@
         <v>2019</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="F315">
         <v>2</v>
@@ -15855,7 +15791,7 @@
         <v>2020</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F316">
         <v>2</v>
@@ -15893,7 +15829,7 @@
         <v>2021</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="F317">
         <v>2</v>
@@ -15931,7 +15867,7 @@
         <v>2022</v>
       </c>
       <c r="E318" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F318">
         <v>2</v>
@@ -15969,7 +15905,7 @@
         <v>2023</v>
       </c>
       <c r="E319" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F319">
         <v>2</v>
@@ -16007,7 +15943,7 @@
         <v>2024</v>
       </c>
       <c r="E320" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F320">
         <v>2</v>
@@ -16045,7 +15981,7 @@
         <v>2025</v>
       </c>
       <c r="E321" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F321">
         <v>2</v>
@@ -16083,7 +16019,7 @@
         <v>2026</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F322" s="3">
         <v>2</v>
@@ -16121,13 +16057,13 @@
         <v>2014</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="F323">
         <v>2</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="H323">
         <v>7</v>
@@ -16159,13 +16095,13 @@
         <v>2015</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F324">
         <v>2</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H324">
         <v>7</v>
@@ -16197,13 +16133,13 @@
         <v>2016</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="F325">
         <v>2</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="H325">
         <v>7</v>
@@ -16235,13 +16171,13 @@
         <v>2017</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F326">
         <v>1</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="H326">
         <v>7</v>
@@ -16273,13 +16209,13 @@
         <v>2018</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F327">
         <v>1</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H327">
         <v>7</v>
@@ -16311,13 +16247,13 @@
         <v>2019</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F328">
         <v>1</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="H328">
         <v>7</v>
@@ -16349,13 +16285,13 @@
         <v>2020</v>
       </c>
       <c r="E329" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="F329">
         <v>1</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H329">
         <v>7</v>
@@ -16387,13 +16323,13 @@
         <v>2021</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="F330">
         <v>1</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="H330">
         <v>7</v>
@@ -16425,13 +16361,13 @@
         <v>2022</v>
       </c>
       <c r="E331" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F331">
         <v>1</v>
       </c>
       <c r="G331" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H331">
         <v>7</v>
@@ -16463,13 +16399,13 @@
         <v>2023</v>
       </c>
       <c r="E332" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F332">
         <v>1</v>
       </c>
       <c r="G332" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H332">
         <v>7</v>
@@ -16501,13 +16437,13 @@
         <v>2024</v>
       </c>
       <c r="E333" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F333">
         <v>2</v>
       </c>
       <c r="G333" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H333">
         <v>7</v>
@@ -16539,13 +16475,13 @@
         <v>2025</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F334" s="3">
         <v>2</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H334" s="3">
         <v>7</v>
@@ -16577,13 +16513,13 @@
         <v>2026</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F335" s="3">
         <v>2</v>
       </c>
       <c r="G335" s="3" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="H335" s="3">
         <v>7</v>
@@ -17603,7 +17539,7 @@
         <v>2014</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F362">
         <v>1</v>
@@ -17641,7 +17577,7 @@
         <v>2015</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F363">
         <v>1</v>
@@ -17679,7 +17615,7 @@
         <v>2016</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="F364">
         <v>1</v>
@@ -17717,7 +17653,7 @@
         <v>2017</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F365">
         <v>1</v>
@@ -17755,7 +17691,7 @@
         <v>2018</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F366">
         <v>1</v>
@@ -17790,7 +17726,7 @@
         <v>2019</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F367">
         <v>1</v>
@@ -17828,7 +17764,7 @@
         <v>2020</v>
       </c>
       <c r="E368" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="F368">
         <v>1</v>
@@ -17866,7 +17802,7 @@
         <v>2021</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F369">
         <v>1</v>
@@ -17904,7 +17840,7 @@
         <v>2022</v>
       </c>
       <c r="E370" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F370">
         <v>1</v>
@@ -17942,7 +17878,7 @@
         <v>2023</v>
       </c>
       <c r="E371" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F371">
         <v>1</v>
@@ -17980,7 +17916,7 @@
         <v>2024</v>
       </c>
       <c r="E372" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F372">
         <v>2</v>
@@ -18018,7 +17954,7 @@
         <v>2025</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F373" s="3">
         <v>2</v>
@@ -18056,7 +17992,7 @@
         <v>2026</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F374" s="3">
         <v>2</v>
@@ -18474,7 +18410,7 @@
         <v>2024</v>
       </c>
       <c r="E385" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F385">
         <v>1</v>
@@ -18512,7 +18448,7 @@
         <v>2025</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F386" s="3">
         <v>1</v>
@@ -18550,7 +18486,7 @@
         <v>2026</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F387" s="3">
         <v>1</v>
@@ -19044,7 +18980,7 @@
         <v>2026</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F400" s="3">
         <v>1</v>
@@ -19196,13 +19132,13 @@
         <v>2017</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="F404">
         <v>1</v>
       </c>
       <c r="G404" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H404">
         <v>0</v>
@@ -19234,7 +19170,7 @@
         <v>2018</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F405">
         <v>1</v>
@@ -19272,7 +19208,7 @@
         <v>2019</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="F406">
         <v>1</v>
@@ -19310,7 +19246,7 @@
         <v>2020</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F407">
         <v>1</v>
@@ -19348,7 +19284,7 @@
         <v>2021</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F408">
         <v>1</v>
@@ -19386,7 +19322,7 @@
         <v>2022</v>
       </c>
       <c r="E409" s="8" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="F409" s="8">
         <v>1</v>
@@ -19424,7 +19360,7 @@
         <v>2023</v>
       </c>
       <c r="E410" s="8" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="F410" s="8">
         <v>1</v>
@@ -19462,7 +19398,7 @@
         <v>2024</v>
       </c>
       <c r="E411" s="8" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="F411" s="8">
         <v>2</v>
@@ -19500,7 +19436,7 @@
         <v>2025</v>
       </c>
       <c r="E412" s="6" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F412" s="6">
         <v>3</v>
@@ -19538,7 +19474,7 @@
         <v>2026</v>
       </c>
       <c r="E413" s="6" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F413" s="6">
         <v>3</v>
@@ -19576,13 +19512,13 @@
         <v>2014</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F414">
         <v>4</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H414">
         <v>7</v>
@@ -19614,13 +19550,13 @@
         <v>2015</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F415">
         <v>4</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="H415">
         <v>7</v>
@@ -19652,13 +19588,13 @@
         <v>2016</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F416">
         <v>3</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="H416">
         <v>7</v>
@@ -19690,13 +19626,13 @@
         <v>2017</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="F417">
         <v>3</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H417">
         <v>7</v>
@@ -19728,13 +19664,13 @@
         <v>2018</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F418">
         <v>3</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H418">
         <v>9</v>
@@ -19766,13 +19702,13 @@
         <v>2019</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="F419">
         <v>4</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="H419">
         <v>9</v>
@@ -19804,13 +19740,13 @@
         <v>2020</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F420">
         <v>4</v>
       </c>
       <c r="G420" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="H420">
         <v>9</v>
@@ -19842,13 +19778,13 @@
         <v>2021</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F421">
         <v>4</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="H421">
         <v>9</v>
@@ -19880,13 +19816,13 @@
         <v>2022</v>
       </c>
       <c r="E422" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F422">
         <v>4</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="H422">
         <v>9</v>
@@ -19918,13 +19854,13 @@
         <v>2023</v>
       </c>
       <c r="E423" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F423">
         <v>5</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="H423">
         <v>9</v>
@@ -19956,13 +19892,13 @@
         <v>2024</v>
       </c>
       <c r="E424" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F424">
         <v>6</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="H424">
         <v>9</v>
@@ -19994,13 +19930,13 @@
         <v>2025</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F425" s="3">
         <v>6</v>
       </c>
       <c r="G425" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="H425" s="3">
         <v>9</v>
@@ -20032,13 +19968,13 @@
         <v>2026</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F426" s="3">
         <v>6</v>
       </c>
       <c r="G426" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="H426" s="3">
         <v>9</v>
@@ -20450,7 +20386,7 @@
         <v>2024</v>
       </c>
       <c r="E437" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F437">
         <v>1</v>
@@ -20488,7 +20424,7 @@
         <v>2025</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F438" s="3">
         <v>1</v>
@@ -20526,7 +20462,7 @@
         <v>2026</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F439" s="3">
         <v>1</v>
@@ -20564,7 +20500,7 @@
         <v>2014</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F440">
         <v>1</v>
@@ -20602,7 +20538,7 @@
         <v>2015</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F441">
         <v>1</v>
@@ -20640,7 +20576,7 @@
         <v>2016</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="F442">
         <v>1</v>
@@ -20678,7 +20614,7 @@
         <v>2017</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F443">
         <v>1</v>
@@ -20716,7 +20652,7 @@
         <v>2018</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="F444">
         <v>1</v>
@@ -20754,7 +20690,7 @@
         <v>2019</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F445">
         <v>1</v>
@@ -20792,7 +20728,7 @@
         <v>2020</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="F446">
         <v>1</v>
@@ -20830,7 +20766,7 @@
         <v>2021</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="F447">
         <v>0</v>
@@ -20944,7 +20880,7 @@
         <v>2024</v>
       </c>
       <c r="E450" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F450">
         <v>1</v>
@@ -20982,7 +20918,7 @@
         <v>2025</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F451" s="3">
         <v>1</v>
@@ -21020,7 +20956,7 @@
         <v>2026</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F452" s="3">
         <v>1</v>
@@ -21058,7 +20994,7 @@
         <v>2014</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="F453">
         <v>3</v>
@@ -21096,7 +21032,7 @@
         <v>2015</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F454">
         <v>3</v>
@@ -21134,7 +21070,7 @@
         <v>2016</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="F455">
         <v>3</v>
@@ -21172,7 +21108,7 @@
         <v>2017</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F456">
         <v>3</v>
@@ -21286,7 +21222,7 @@
         <v>2020</v>
       </c>
       <c r="E459" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="F459">
         <v>1</v>
@@ -21324,7 +21260,7 @@
         <v>2021</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="F460">
         <v>1</v>
@@ -21362,7 +21298,7 @@
         <v>2022</v>
       </c>
       <c r="E461" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F461">
         <v>1</v>
@@ -21400,7 +21336,7 @@
         <v>2023</v>
       </c>
       <c r="E462" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F462">
         <v>1</v>
@@ -21438,7 +21374,7 @@
         <v>2024</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="F463" s="3">
         <v>3</v>
@@ -21476,7 +21412,7 @@
         <v>2025</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="F464" s="3">
         <v>4</v>
@@ -21514,7 +21450,7 @@
         <v>2026</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="F465" s="3">
         <v>4</v>
@@ -21932,7 +21868,7 @@
         <v>2024</v>
       </c>
       <c r="E476" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F476">
         <v>1</v>
@@ -21970,7 +21906,7 @@
         <v>2025</v>
       </c>
       <c r="E477" s="3" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="F477" s="3">
         <v>2</v>
@@ -21994,39 +21930,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A478" t="s">
-        <v>115</v>
-      </c>
-      <c r="B478" t="s">
-        <v>116</v>
-      </c>
-      <c r="C478" t="s">
-        <v>36</v>
-      </c>
-      <c r="D478">
-        <v>2014</v>
-      </c>
-      <c r="E478" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="F478">
-        <v>1</v>
-      </c>
-      <c r="G478" t="s">
-        <v>126</v>
-      </c>
-      <c r="H478">
-        <v>0</v>
-      </c>
-      <c r="I478">
-        <v>0</v>
-      </c>
-      <c r="J478">
-        <v>0</v>
-      </c>
-      <c r="K478">
-        <v>0</v>
+    <row r="478" spans="1:12" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A478" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B478" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D478" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E478" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F478" s="3">
+        <v>2</v>
+      </c>
+      <c r="G478" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H478" s="3">
+        <v>0</v>
+      </c>
+      <c r="I478" s="3">
+        <v>0</v>
+      </c>
+      <c r="J478" s="3">
+        <v>0</v>
+      </c>
+      <c r="K478" s="3">
+        <v>0</v>
+      </c>
+      <c r="L478" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="479" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
@@ -22040,10 +21979,10 @@
         <v>36</v>
       </c>
       <c r="D479">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="F479">
         <v>1</v>
@@ -22075,10 +22014,10 @@
         <v>36</v>
       </c>
       <c r="D480">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="F480">
         <v>1</v>
@@ -22110,10 +22049,10 @@
         <v>36</v>
       </c>
       <c r="D481">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F481">
         <v>1</v>
@@ -22145,13 +22084,13 @@
         <v>36</v>
       </c>
       <c r="D482">
-        <v>2018</v>
-      </c>
-      <c r="E482" t="s">
-        <v>351</v>
+        <v>2017</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="F482">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G482" t="s">
         <v>126</v>
@@ -22180,10 +22119,10 @@
         <v>36</v>
       </c>
       <c r="D483">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E483" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="F483">
         <v>2</v>
@@ -22215,10 +22154,10 @@
         <v>36</v>
       </c>
       <c r="D484">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E484" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="F484">
         <v>2</v>
@@ -22250,10 +22189,10 @@
         <v>36</v>
       </c>
       <c r="D485">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E485" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="F485">
         <v>2</v>
@@ -22272,9 +22211,6 @@
       </c>
       <c r="K485">
         <v>0</v>
-      </c>
-      <c r="L485">
-        <v>2</v>
       </c>
     </row>
     <row r="486" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
@@ -22288,10 +22224,10 @@
         <v>36</v>
       </c>
       <c r="D486">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E486" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="F486">
         <v>2</v>
@@ -22311,7 +22247,9 @@
       <c r="K486">
         <v>0</v>
       </c>
-      <c r="L486" s="5"/>
+      <c r="L486">
+        <v>2</v>
+      </c>
     </row>
     <row r="487" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A487" t="s">
@@ -22324,10 +22262,10 @@
         <v>36</v>
       </c>
       <c r="D487">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E487" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="F487">
         <v>2</v>
@@ -22360,2985 +22298,146 @@
         <v>36</v>
       </c>
       <c r="D488">
+        <v>2023</v>
+      </c>
+      <c r="E488" t="s">
+        <v>361</v>
+      </c>
+      <c r="F488">
+        <v>2</v>
+      </c>
+      <c r="G488" t="s">
+        <v>126</v>
+      </c>
+      <c r="H488">
+        <v>0</v>
+      </c>
+      <c r="I488">
+        <v>0</v>
+      </c>
+      <c r="J488">
+        <v>0</v>
+      </c>
+      <c r="K488">
+        <v>0</v>
+      </c>
+      <c r="L488" s="5"/>
+    </row>
+    <row r="489" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A489" t="s">
+        <v>115</v>
+      </c>
+      <c r="B489" t="s">
+        <v>116</v>
+      </c>
+      <c r="C489" t="s">
+        <v>36</v>
+      </c>
+      <c r="D489">
         <v>2024</v>
       </c>
-      <c r="E488" t="s">
-        <v>371</v>
-      </c>
-      <c r="F488">
-        <v>2</v>
-      </c>
-      <c r="G488" t="s">
-        <v>126</v>
-      </c>
-      <c r="H488">
-        <v>0</v>
-      </c>
-      <c r="I488">
-        <v>0</v>
-      </c>
-      <c r="J488">
-        <v>0</v>
-      </c>
-      <c r="K488">
-        <v>0</v>
-      </c>
-      <c r="L488" s="5"/>
-    </row>
-    <row r="489" spans="1:12" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A489" s="3" t="s">
+      <c r="E489" t="s">
+        <v>361</v>
+      </c>
+      <c r="F489">
+        <v>2</v>
+      </c>
+      <c r="G489" t="s">
+        <v>126</v>
+      </c>
+      <c r="H489">
+        <v>0</v>
+      </c>
+      <c r="I489">
+        <v>0</v>
+      </c>
+      <c r="J489">
+        <v>0</v>
+      </c>
+      <c r="K489">
+        <v>0</v>
+      </c>
+      <c r="L489" s="5"/>
+    </row>
+    <row r="490" spans="1:12" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A490" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B489" s="3" t="s">
+      <c r="B490" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C489" s="3" t="s">
+      <c r="C490" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D489" s="3">
+      <c r="D490" s="3">
         <v>2024</v>
       </c>
-      <c r="E489" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F489" s="3">
-        <v>2</v>
-      </c>
-      <c r="G489" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H489" s="3">
-        <v>0</v>
-      </c>
-      <c r="I489" s="3">
-        <v>0</v>
-      </c>
-      <c r="J489" s="3">
-        <v>0</v>
-      </c>
-      <c r="K489" s="3">
+      <c r="E490" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F490" s="3">
+        <v>2</v>
+      </c>
+      <c r="G490" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H490" s="3">
+        <v>0</v>
+      </c>
+      <c r="I490" s="3">
+        <v>0</v>
+      </c>
+      <c r="J490" s="3">
+        <v>0</v>
+      </c>
+      <c r="K490" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:12" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A491" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D491" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E491" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F491" s="3">
+        <v>2</v>
+      </c>
+      <c r="G491" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H491" s="3">
+        <v>0</v>
+      </c>
+      <c r="I491" s="3">
+        <v>0</v>
+      </c>
+      <c r="J491" s="3">
+        <v>0</v>
+      </c>
+      <c r="K491" s="3">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L489" xr:uid="{3C2DF56A-1A76-4E35-AC1A-4D6FF403CC05}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:L489">
-      <sortCondition ref="A1:A489"/>
+  <autoFilter ref="A1:L490" xr:uid="{3C2DF56A-1A76-4E35-AC1A-4D6FF403CC05}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:L490">
+      <sortCondition ref="A1:A490"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BEE7638-9852-4D6D-B211-E19B1C07A12F}">
-  <dimension ref="A1:C267"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.65"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>2014</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2014</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>2014</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>2014</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>2014</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>2014</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>2014</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>2014</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>2014</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>2014</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>2014</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>2014</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15">
-        <v>2014</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16">
-        <v>2014</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17">
-        <v>2014</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18">
-        <v>2014</v>
-      </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19">
-        <v>2014</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20">
-        <v>2014</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21">
-        <v>2014</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22">
-        <v>2014</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23">
-        <v>2014</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24">
-        <v>2014</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25">
-        <v>2014</v>
-      </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26">
-        <v>2014</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27">
-        <v>2014</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28">
-        <v>2014</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29">
-        <v>2014</v>
-      </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30">
-        <v>2014</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31">
-        <v>2014</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32">
-        <v>2014</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33">
-        <v>2014</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34">
-        <v>2014</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35">
-        <v>2014</v>
-      </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36">
-        <v>2014</v>
-      </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37">
-        <v>2014</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38">
-        <v>2014</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40">
-        <v>2015</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41">
-        <v>2015</v>
-      </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A42" t="s">
-        <v>2</v>
-      </c>
-      <c r="B42">
-        <v>2015</v>
-      </c>
-      <c r="C42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A43" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43">
-        <v>2015</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A44" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44">
-        <v>2015</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45">
-        <v>2015</v>
-      </c>
-      <c r="C45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A46" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47">
-        <v>2015</v>
-      </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A48" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48">
-        <v>2015</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A49" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49">
-        <v>2015</v>
-      </c>
-      <c r="C49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50">
-        <v>2015</v>
-      </c>
-      <c r="C50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51">
-        <v>2015</v>
-      </c>
-      <c r="C51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A52" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52">
-        <v>2015</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53">
-        <v>2015</v>
-      </c>
-      <c r="C53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A54" t="s">
-        <v>13</v>
-      </c>
-      <c r="B54">
-        <v>2015</v>
-      </c>
-      <c r="C54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A55" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55">
-        <v>2015</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56">
-        <v>2015</v>
-      </c>
-      <c r="C56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A57" t="s">
-        <v>16</v>
-      </c>
-      <c r="B57">
-        <v>2015</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A58" t="s">
-        <v>17</v>
-      </c>
-      <c r="B58">
-        <v>2015</v>
-      </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A59" t="s">
-        <v>18</v>
-      </c>
-      <c r="B59">
-        <v>2015</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A60" t="s">
-        <v>19</v>
-      </c>
-      <c r="B60">
-        <v>2015</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A61" t="s">
-        <v>20</v>
-      </c>
-      <c r="B61">
-        <v>2015</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A62" t="s">
-        <v>21</v>
-      </c>
-      <c r="B62">
-        <v>2015</v>
-      </c>
-      <c r="C62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A63" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63">
-        <v>2015</v>
-      </c>
-      <c r="C63">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A64" t="s">
-        <v>23</v>
-      </c>
-      <c r="B64">
-        <v>2015</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A65" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65">
-        <v>2015</v>
-      </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A66" t="s">
-        <v>25</v>
-      </c>
-      <c r="B66">
-        <v>2015</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A67" t="s">
-        <v>26</v>
-      </c>
-      <c r="B67">
-        <v>2015</v>
-      </c>
-      <c r="C67">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A68" t="s">
-        <v>27</v>
-      </c>
-      <c r="B68">
-        <v>2015</v>
-      </c>
-      <c r="C68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B69">
-        <v>2015</v>
-      </c>
-      <c r="C69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A70" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70">
-        <v>2015</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A71" t="s">
-        <v>30</v>
-      </c>
-      <c r="B71">
-        <v>2015</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A72" t="s">
-        <v>31</v>
-      </c>
-      <c r="B72">
-        <v>2015</v>
-      </c>
-      <c r="C72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A73" t="s">
-        <v>32</v>
-      </c>
-      <c r="B73">
-        <v>2015</v>
-      </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B74">
-        <v>2015</v>
-      </c>
-      <c r="C74">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A75" t="s">
-        <v>34</v>
-      </c>
-      <c r="B75">
-        <v>2015</v>
-      </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A76" t="s">
-        <v>35</v>
-      </c>
-      <c r="B76">
-        <v>2015</v>
-      </c>
-      <c r="C76">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A77" t="s">
-        <v>36</v>
-      </c>
-      <c r="B77">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B78">
-        <v>2016</v>
-      </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A79" t="s">
-        <v>1</v>
-      </c>
-      <c r="B79">
-        <v>2016</v>
-      </c>
-      <c r="C79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A80" t="s">
-        <v>2</v>
-      </c>
-      <c r="B80">
-        <v>2016</v>
-      </c>
-      <c r="C80">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A81" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81">
-        <v>2016</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A82" t="s">
-        <v>4</v>
-      </c>
-      <c r="B82">
-        <v>2016</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A83" t="s">
-        <v>5</v>
-      </c>
-      <c r="B83">
-        <v>2016</v>
-      </c>
-      <c r="C83">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A84" t="s">
-        <v>37</v>
-      </c>
-      <c r="B84">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A85" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85">
-        <v>2016</v>
-      </c>
-      <c r="C85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A86" t="s">
-        <v>7</v>
-      </c>
-      <c r="B86">
-        <v>2016</v>
-      </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A87" t="s">
-        <v>8</v>
-      </c>
-      <c r="B87">
-        <v>2016</v>
-      </c>
-      <c r="C87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A88" t="s">
-        <v>9</v>
-      </c>
-      <c r="B88">
-        <v>2016</v>
-      </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A89" t="s">
-        <v>10</v>
-      </c>
-      <c r="B89">
-        <v>2016</v>
-      </c>
-      <c r="C89">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A90" t="s">
-        <v>11</v>
-      </c>
-      <c r="B90">
-        <v>2016</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A91" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91">
-        <v>2016</v>
-      </c>
-      <c r="C91">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A92" t="s">
-        <v>13</v>
-      </c>
-      <c r="B92">
-        <v>2016</v>
-      </c>
-      <c r="C92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A93" t="s">
-        <v>14</v>
-      </c>
-      <c r="B93">
-        <v>2016</v>
-      </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94">
-        <v>2016</v>
-      </c>
-      <c r="C94">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A95" t="s">
-        <v>16</v>
-      </c>
-      <c r="B95">
-        <v>2016</v>
-      </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A96" t="s">
-        <v>17</v>
-      </c>
-      <c r="B96">
-        <v>2016</v>
-      </c>
-      <c r="C96">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A97" t="s">
-        <v>18</v>
-      </c>
-      <c r="B97">
-        <v>2016</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A98" t="s">
-        <v>19</v>
-      </c>
-      <c r="B98">
-        <v>2016</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A99" t="s">
-        <v>20</v>
-      </c>
-      <c r="B99">
-        <v>2016</v>
-      </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A100" t="s">
-        <v>21</v>
-      </c>
-      <c r="B100">
-        <v>2016</v>
-      </c>
-      <c r="C100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A101" t="s">
-        <v>22</v>
-      </c>
-      <c r="B101">
-        <v>2016</v>
-      </c>
-      <c r="C101">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A102" t="s">
-        <v>23</v>
-      </c>
-      <c r="B102">
-        <v>2016</v>
-      </c>
-      <c r="C102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A103" t="s">
-        <v>24</v>
-      </c>
-      <c r="B103">
-        <v>2016</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A104" t="s">
-        <v>25</v>
-      </c>
-      <c r="B104">
-        <v>2016</v>
-      </c>
-      <c r="C104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A105" t="s">
-        <v>26</v>
-      </c>
-      <c r="B105">
-        <v>2016</v>
-      </c>
-      <c r="C105">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A106" t="s">
-        <v>27</v>
-      </c>
-      <c r="B106">
-        <v>2016</v>
-      </c>
-      <c r="C106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A107" t="s">
-        <v>28</v>
-      </c>
-      <c r="B107">
-        <v>2016</v>
-      </c>
-      <c r="C107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A108" t="s">
-        <v>29</v>
-      </c>
-      <c r="B108">
-        <v>2016</v>
-      </c>
-      <c r="C108">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A109" t="s">
-        <v>30</v>
-      </c>
-      <c r="B109">
-        <v>2016</v>
-      </c>
-      <c r="C109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A110" t="s">
-        <v>31</v>
-      </c>
-      <c r="B110">
-        <v>2016</v>
-      </c>
-      <c r="C110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A111" t="s">
-        <v>32</v>
-      </c>
-      <c r="B111">
-        <v>2016</v>
-      </c>
-      <c r="C111">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A112" t="s">
-        <v>33</v>
-      </c>
-      <c r="B112">
-        <v>2016</v>
-      </c>
-      <c r="C112">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A113" t="s">
-        <v>34</v>
-      </c>
-      <c r="B113">
-        <v>2016</v>
-      </c>
-      <c r="C113">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A114" t="s">
-        <v>35</v>
-      </c>
-      <c r="B114">
-        <v>2016</v>
-      </c>
-      <c r="C114">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A115" t="s">
-        <v>36</v>
-      </c>
-      <c r="B115">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B116">
-        <v>2017</v>
-      </c>
-      <c r="C116">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A117" t="s">
-        <v>1</v>
-      </c>
-      <c r="B117">
-        <v>2017</v>
-      </c>
-      <c r="C117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A118" t="s">
-        <v>2</v>
-      </c>
-      <c r="B118">
-        <v>2017</v>
-      </c>
-      <c r="C118">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A119" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119">
-        <v>2017</v>
-      </c>
-      <c r="C119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A120" t="s">
-        <v>4</v>
-      </c>
-      <c r="B120">
-        <v>2017</v>
-      </c>
-      <c r="C120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A121" t="s">
-        <v>5</v>
-      </c>
-      <c r="B121">
-        <v>2017</v>
-      </c>
-      <c r="C121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A122" t="s">
-        <v>37</v>
-      </c>
-      <c r="B122">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A123" t="s">
-        <v>6</v>
-      </c>
-      <c r="B123">
-        <v>2017</v>
-      </c>
-      <c r="C123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A124" t="s">
-        <v>7</v>
-      </c>
-      <c r="B124">
-        <v>2017</v>
-      </c>
-      <c r="C124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A125" t="s">
-        <v>8</v>
-      </c>
-      <c r="B125">
-        <v>2017</v>
-      </c>
-      <c r="C125">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A126" t="s">
-        <v>9</v>
-      </c>
-      <c r="B126">
-        <v>2017</v>
-      </c>
-      <c r="C126">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A127" t="s">
-        <v>10</v>
-      </c>
-      <c r="B127">
-        <v>2017</v>
-      </c>
-      <c r="C127">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A128" t="s">
-        <v>11</v>
-      </c>
-      <c r="B128">
-        <v>2017</v>
-      </c>
-      <c r="C128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A129" t="s">
-        <v>12</v>
-      </c>
-      <c r="B129">
-        <v>2017</v>
-      </c>
-      <c r="C129">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A130" t="s">
-        <v>13</v>
-      </c>
-      <c r="B130">
-        <v>2017</v>
-      </c>
-      <c r="C130">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A131" t="s">
-        <v>14</v>
-      </c>
-      <c r="B131">
-        <v>2017</v>
-      </c>
-      <c r="C131">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132">
-        <v>2017</v>
-      </c>
-      <c r="C132">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A133" t="s">
-        <v>16</v>
-      </c>
-      <c r="B133">
-        <v>2017</v>
-      </c>
-      <c r="C133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A134" t="s">
-        <v>17</v>
-      </c>
-      <c r="B134">
-        <v>2017</v>
-      </c>
-      <c r="C134">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A135" t="s">
-        <v>18</v>
-      </c>
-      <c r="B135">
-        <v>2017</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A136" t="s">
-        <v>19</v>
-      </c>
-      <c r="B136">
-        <v>2017</v>
-      </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A137" t="s">
-        <v>20</v>
-      </c>
-      <c r="B137">
-        <v>2017</v>
-      </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A138" t="s">
-        <v>21</v>
-      </c>
-      <c r="B138">
-        <v>2017</v>
-      </c>
-      <c r="C138">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A139" t="s">
-        <v>22</v>
-      </c>
-      <c r="B139">
-        <v>2017</v>
-      </c>
-      <c r="C139">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A140" t="s">
-        <v>23</v>
-      </c>
-      <c r="B140">
-        <v>2017</v>
-      </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A141" t="s">
-        <v>24</v>
-      </c>
-      <c r="B141">
-        <v>2017</v>
-      </c>
-      <c r="C141">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A142" t="s">
-        <v>25</v>
-      </c>
-      <c r="B142">
-        <v>2017</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A143" t="s">
-        <v>26</v>
-      </c>
-      <c r="B143">
-        <v>2017</v>
-      </c>
-      <c r="C143">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A144" t="s">
-        <v>27</v>
-      </c>
-      <c r="B144">
-        <v>2017</v>
-      </c>
-      <c r="C144">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A145" t="s">
-        <v>28</v>
-      </c>
-      <c r="B145">
-        <v>2017</v>
-      </c>
-      <c r="C145">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A146" t="s">
-        <v>29</v>
-      </c>
-      <c r="B146">
-        <v>2017</v>
-      </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A147" t="s">
-        <v>30</v>
-      </c>
-      <c r="B147">
-        <v>2017</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A148" t="s">
-        <v>31</v>
-      </c>
-      <c r="B148">
-        <v>2017</v>
-      </c>
-      <c r="C148">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A149" t="s">
-        <v>32</v>
-      </c>
-      <c r="B149">
-        <v>2017</v>
-      </c>
-      <c r="C149">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A150" t="s">
-        <v>33</v>
-      </c>
-      <c r="B150">
-        <v>2017</v>
-      </c>
-      <c r="C150">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A151" t="s">
-        <v>34</v>
-      </c>
-      <c r="B151">
-        <v>2017</v>
-      </c>
-      <c r="C151">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A152" t="s">
-        <v>35</v>
-      </c>
-      <c r="B152">
-        <v>2017</v>
-      </c>
-      <c r="C152">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A153" t="s">
-        <v>36</v>
-      </c>
-      <c r="B153">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A154" t="s">
-        <v>0</v>
-      </c>
-      <c r="B154">
-        <v>2018</v>
-      </c>
-      <c r="C154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A155" t="s">
-        <v>1</v>
-      </c>
-      <c r="B155">
-        <v>2018</v>
-      </c>
-      <c r="C155">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A156" t="s">
-        <v>2</v>
-      </c>
-      <c r="B156">
-        <v>2018</v>
-      </c>
-      <c r="C156">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A157" t="s">
-        <v>3</v>
-      </c>
-      <c r="B157">
-        <v>2018</v>
-      </c>
-      <c r="C157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A158" t="s">
-        <v>4</v>
-      </c>
-      <c r="B158">
-        <v>2018</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A159" t="s">
-        <v>5</v>
-      </c>
-      <c r="B159">
-        <v>2018</v>
-      </c>
-      <c r="C159">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A160" t="s">
-        <v>37</v>
-      </c>
-      <c r="B160">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A161" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161">
-        <v>2018</v>
-      </c>
-      <c r="C161">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A162" t="s">
-        <v>7</v>
-      </c>
-      <c r="B162">
-        <v>2018</v>
-      </c>
-      <c r="C162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A163" t="s">
-        <v>8</v>
-      </c>
-      <c r="B163">
-        <v>2018</v>
-      </c>
-      <c r="C163">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A164" t="s">
-        <v>9</v>
-      </c>
-      <c r="B164">
-        <v>2018</v>
-      </c>
-      <c r="C164">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A165" t="s">
-        <v>10</v>
-      </c>
-      <c r="B165">
-        <v>2018</v>
-      </c>
-      <c r="C165">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A166" t="s">
-        <v>11</v>
-      </c>
-      <c r="B166">
-        <v>2018</v>
-      </c>
-      <c r="C166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A167" t="s">
-        <v>12</v>
-      </c>
-      <c r="B167">
-        <v>2018</v>
-      </c>
-      <c r="C167">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A168" t="s">
-        <v>13</v>
-      </c>
-      <c r="B168">
-        <v>2018</v>
-      </c>
-      <c r="C168">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A169" t="s">
-        <v>14</v>
-      </c>
-      <c r="B169">
-        <v>2018</v>
-      </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170">
-        <v>2018</v>
-      </c>
-      <c r="C170">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A171" t="s">
-        <v>16</v>
-      </c>
-      <c r="B171">
-        <v>2018</v>
-      </c>
-      <c r="C171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A172" t="s">
-        <v>17</v>
-      </c>
-      <c r="B172">
-        <v>2018</v>
-      </c>
-      <c r="C172">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A173" t="s">
-        <v>18</v>
-      </c>
-      <c r="B173">
-        <v>2018</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A174" t="s">
-        <v>19</v>
-      </c>
-      <c r="B174">
-        <v>2018</v>
-      </c>
-      <c r="C174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A175" t="s">
-        <v>20</v>
-      </c>
-      <c r="B175">
-        <v>2018</v>
-      </c>
-      <c r="C175">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A176" t="s">
-        <v>21</v>
-      </c>
-      <c r="B176">
-        <v>2018</v>
-      </c>
-      <c r="C176">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A177" t="s">
-        <v>22</v>
-      </c>
-      <c r="B177">
-        <v>2018</v>
-      </c>
-      <c r="C177">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A178" t="s">
-        <v>23</v>
-      </c>
-      <c r="B178">
-        <v>2018</v>
-      </c>
-      <c r="C178">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A179" t="s">
-        <v>24</v>
-      </c>
-      <c r="B179">
-        <v>2018</v>
-      </c>
-      <c r="C179">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A180" t="s">
-        <v>25</v>
-      </c>
-      <c r="B180">
-        <v>2018</v>
-      </c>
-      <c r="C180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A181" t="s">
-        <v>26</v>
-      </c>
-      <c r="B181">
-        <v>2018</v>
-      </c>
-      <c r="C181">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A182" t="s">
-        <v>27</v>
-      </c>
-      <c r="B182">
-        <v>2018</v>
-      </c>
-      <c r="C182">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A183" t="s">
-        <v>28</v>
-      </c>
-      <c r="B183">
-        <v>2018</v>
-      </c>
-      <c r="C183">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A184" t="s">
-        <v>29</v>
-      </c>
-      <c r="B184">
-        <v>2018</v>
-      </c>
-      <c r="C184">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A185" t="s">
-        <v>30</v>
-      </c>
-      <c r="B185">
-        <v>2018</v>
-      </c>
-      <c r="C185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A186" t="s">
-        <v>31</v>
-      </c>
-      <c r="B186">
-        <v>2018</v>
-      </c>
-      <c r="C186">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A187" t="s">
-        <v>32</v>
-      </c>
-      <c r="B187">
-        <v>2018</v>
-      </c>
-      <c r="C187">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A188" t="s">
-        <v>33</v>
-      </c>
-      <c r="B188">
-        <v>2018</v>
-      </c>
-      <c r="C188">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A189" t="s">
-        <v>34</v>
-      </c>
-      <c r="B189">
-        <v>2018</v>
-      </c>
-      <c r="C189">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A190" t="s">
-        <v>35</v>
-      </c>
-      <c r="B190">
-        <v>2018</v>
-      </c>
-      <c r="C190">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A191" t="s">
-        <v>36</v>
-      </c>
-      <c r="B191">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A192" t="s">
-        <v>0</v>
-      </c>
-      <c r="B192">
-        <v>2019</v>
-      </c>
-      <c r="C192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A193" t="s">
-        <v>1</v>
-      </c>
-      <c r="B193">
-        <v>2019</v>
-      </c>
-      <c r="C193">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A194" t="s">
-        <v>2</v>
-      </c>
-      <c r="B194">
-        <v>2019</v>
-      </c>
-      <c r="C194">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A195" t="s">
-        <v>3</v>
-      </c>
-      <c r="B195">
-        <v>2019</v>
-      </c>
-      <c r="C195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A196" t="s">
-        <v>4</v>
-      </c>
-      <c r="B196">
-        <v>2019</v>
-      </c>
-      <c r="C196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A197" t="s">
-        <v>5</v>
-      </c>
-      <c r="B197">
-        <v>2019</v>
-      </c>
-      <c r="C197">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A198" t="s">
-        <v>37</v>
-      </c>
-      <c r="B198">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A199" t="s">
-        <v>6</v>
-      </c>
-      <c r="B199">
-        <v>2019</v>
-      </c>
-      <c r="C199">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A200" t="s">
-        <v>7</v>
-      </c>
-      <c r="B200">
-        <v>2019</v>
-      </c>
-      <c r="C200">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A201" t="s">
-        <v>8</v>
-      </c>
-      <c r="B201">
-        <v>2019</v>
-      </c>
-      <c r="C201">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A202" t="s">
-        <v>9</v>
-      </c>
-      <c r="B202">
-        <v>2019</v>
-      </c>
-      <c r="C202">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A203" t="s">
-        <v>10</v>
-      </c>
-      <c r="B203">
-        <v>2019</v>
-      </c>
-      <c r="C203">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A204" t="s">
-        <v>11</v>
-      </c>
-      <c r="B204">
-        <v>2019</v>
-      </c>
-      <c r="C204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A205" t="s">
-        <v>12</v>
-      </c>
-      <c r="B205">
-        <v>2019</v>
-      </c>
-      <c r="C205">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A206" t="s">
-        <v>13</v>
-      </c>
-      <c r="B206">
-        <v>2019</v>
-      </c>
-      <c r="C206">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A207" t="s">
-        <v>14</v>
-      </c>
-      <c r="B207">
-        <v>2019</v>
-      </c>
-      <c r="C207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A208" t="s">
-        <v>15</v>
-      </c>
-      <c r="B208">
-        <v>2019</v>
-      </c>
-      <c r="C208">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A209" t="s">
-        <v>16</v>
-      </c>
-      <c r="B209">
-        <v>2019</v>
-      </c>
-      <c r="C209">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A210" t="s">
-        <v>17</v>
-      </c>
-      <c r="B210">
-        <v>2019</v>
-      </c>
-      <c r="C210">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A211" t="s">
-        <v>18</v>
-      </c>
-      <c r="B211">
-        <v>2019</v>
-      </c>
-      <c r="C211">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A212" t="s">
-        <v>19</v>
-      </c>
-      <c r="B212">
-        <v>2019</v>
-      </c>
-      <c r="C212">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A213" t="s">
-        <v>20</v>
-      </c>
-      <c r="B213">
-        <v>2019</v>
-      </c>
-      <c r="C213">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A214" t="s">
-        <v>21</v>
-      </c>
-      <c r="B214">
-        <v>2019</v>
-      </c>
-      <c r="C214">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A215" t="s">
-        <v>22</v>
-      </c>
-      <c r="B215">
-        <v>2019</v>
-      </c>
-      <c r="C215">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A216" t="s">
-        <v>23</v>
-      </c>
-      <c r="B216">
-        <v>2019</v>
-      </c>
-      <c r="C216">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A217" t="s">
-        <v>24</v>
-      </c>
-      <c r="B217">
-        <v>2019</v>
-      </c>
-      <c r="C217">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A218" t="s">
-        <v>25</v>
-      </c>
-      <c r="B218">
-        <v>2019</v>
-      </c>
-      <c r="C218">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A219" t="s">
-        <v>26</v>
-      </c>
-      <c r="B219">
-        <v>2019</v>
-      </c>
-      <c r="C219">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A220" t="s">
-        <v>27</v>
-      </c>
-      <c r="B220">
-        <v>2019</v>
-      </c>
-      <c r="C220">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A221" t="s">
-        <v>28</v>
-      </c>
-      <c r="B221">
-        <v>2019</v>
-      </c>
-      <c r="C221">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A222" t="s">
-        <v>29</v>
-      </c>
-      <c r="B222">
-        <v>2019</v>
-      </c>
-      <c r="C222">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A223" t="s">
-        <v>30</v>
-      </c>
-      <c r="B223">
-        <v>2019</v>
-      </c>
-      <c r="C223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A224" t="s">
-        <v>31</v>
-      </c>
-      <c r="B224">
-        <v>2019</v>
-      </c>
-      <c r="C224">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A225" t="s">
-        <v>32</v>
-      </c>
-      <c r="B225">
-        <v>2019</v>
-      </c>
-      <c r="C225">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A226" t="s">
-        <v>33</v>
-      </c>
-      <c r="B226">
-        <v>2019</v>
-      </c>
-      <c r="C226">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A227" t="s">
-        <v>34</v>
-      </c>
-      <c r="B227">
-        <v>2019</v>
-      </c>
-      <c r="C227">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A228" t="s">
-        <v>35</v>
-      </c>
-      <c r="B228">
-        <v>2019</v>
-      </c>
-      <c r="C228">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A229" t="s">
-        <v>36</v>
-      </c>
-      <c r="B229">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A230" t="s">
-        <v>0</v>
-      </c>
-      <c r="B230">
-        <v>2020</v>
-      </c>
-      <c r="C230">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A231" t="s">
-        <v>1</v>
-      </c>
-      <c r="B231">
-        <v>2020</v>
-      </c>
-      <c r="C231">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A232" t="s">
-        <v>2</v>
-      </c>
-      <c r="B232">
-        <v>2020</v>
-      </c>
-      <c r="C232">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A233" t="s">
-        <v>3</v>
-      </c>
-      <c r="B233">
-        <v>2020</v>
-      </c>
-      <c r="C233">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A234" t="s">
-        <v>4</v>
-      </c>
-      <c r="B234">
-        <v>2020</v>
-      </c>
-      <c r="C234">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A235" t="s">
-        <v>5</v>
-      </c>
-      <c r="B235">
-        <v>2020</v>
-      </c>
-      <c r="C235">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A236" t="s">
-        <v>37</v>
-      </c>
-      <c r="B236">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A237" t="s">
-        <v>6</v>
-      </c>
-      <c r="B237">
-        <v>2020</v>
-      </c>
-      <c r="C237">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A238" t="s">
-        <v>7</v>
-      </c>
-      <c r="B238">
-        <v>2020</v>
-      </c>
-      <c r="C238">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A239" t="s">
-        <v>8</v>
-      </c>
-      <c r="B239">
-        <v>2020</v>
-      </c>
-      <c r="C239">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A240" t="s">
-        <v>9</v>
-      </c>
-      <c r="B240">
-        <v>2020</v>
-      </c>
-      <c r="C240">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A241" t="s">
-        <v>10</v>
-      </c>
-      <c r="B241">
-        <v>2020</v>
-      </c>
-      <c r="C241">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A242" t="s">
-        <v>11</v>
-      </c>
-      <c r="B242">
-        <v>2020</v>
-      </c>
-      <c r="C242">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A243" t="s">
-        <v>12</v>
-      </c>
-      <c r="B243">
-        <v>2020</v>
-      </c>
-      <c r="C243">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A244" t="s">
-        <v>13</v>
-      </c>
-      <c r="B244">
-        <v>2020</v>
-      </c>
-      <c r="C244">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A245" t="s">
-        <v>14</v>
-      </c>
-      <c r="B245">
-        <v>2020</v>
-      </c>
-      <c r="C245">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A246" t="s">
-        <v>15</v>
-      </c>
-      <c r="B246">
-        <v>2020</v>
-      </c>
-      <c r="C246">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A247" t="s">
-        <v>16</v>
-      </c>
-      <c r="B247">
-        <v>2020</v>
-      </c>
-      <c r="C247">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A248" t="s">
-        <v>17</v>
-      </c>
-      <c r="B248">
-        <v>2020</v>
-      </c>
-      <c r="C248">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A249" t="s">
-        <v>18</v>
-      </c>
-      <c r="B249">
-        <v>2020</v>
-      </c>
-      <c r="C249">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A250" t="s">
-        <v>19</v>
-      </c>
-      <c r="B250">
-        <v>2020</v>
-      </c>
-      <c r="C250">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A251" t="s">
-        <v>20</v>
-      </c>
-      <c r="B251">
-        <v>2020</v>
-      </c>
-      <c r="C251">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A252" t="s">
-        <v>21</v>
-      </c>
-      <c r="B252">
-        <v>2020</v>
-      </c>
-      <c r="C252">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A253" t="s">
-        <v>22</v>
-      </c>
-      <c r="B253">
-        <v>2020</v>
-      </c>
-      <c r="C253">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A254" t="s">
-        <v>23</v>
-      </c>
-      <c r="B254">
-        <v>2020</v>
-      </c>
-      <c r="C254">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A255" t="s">
-        <v>24</v>
-      </c>
-      <c r="B255">
-        <v>2020</v>
-      </c>
-      <c r="C255">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A256" t="s">
-        <v>25</v>
-      </c>
-      <c r="B256">
-        <v>2020</v>
-      </c>
-      <c r="C256">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A257" t="s">
-        <v>26</v>
-      </c>
-      <c r="B257">
-        <v>2020</v>
-      </c>
-      <c r="C257">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A258" t="s">
-        <v>27</v>
-      </c>
-      <c r="B258">
-        <v>2020</v>
-      </c>
-      <c r="C258">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A259" t="s">
-        <v>28</v>
-      </c>
-      <c r="B259">
-        <v>2020</v>
-      </c>
-      <c r="C259">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A260" t="s">
-        <v>29</v>
-      </c>
-      <c r="B260">
-        <v>2020</v>
-      </c>
-      <c r="C260">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A261" t="s">
-        <v>30</v>
-      </c>
-      <c r="B261">
-        <v>2020</v>
-      </c>
-      <c r="C261">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A262" t="s">
-        <v>31</v>
-      </c>
-      <c r="B262">
-        <v>2020</v>
-      </c>
-      <c r="C262">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A263" t="s">
-        <v>32</v>
-      </c>
-      <c r="B263">
-        <v>2020</v>
-      </c>
-      <c r="C263">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A264" t="s">
-        <v>33</v>
-      </c>
-      <c r="B264">
-        <v>2020</v>
-      </c>
-      <c r="C264">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A265" t="s">
-        <v>34</v>
-      </c>
-      <c r="B265">
-        <v>2020</v>
-      </c>
-      <c r="C265">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A266" t="s">
-        <v>35</v>
-      </c>
-      <c r="B266">
-        <v>2020</v>
-      </c>
-      <c r="C266">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.65">
-      <c r="A267" t="s">
-        <v>36</v>
-      </c>
-      <c r="B267">
-        <v>2020</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C253" xr:uid="{3BEE7638-9852-4D6D-B211-E19B1C07A12F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C267">
-      <sortCondition ref="B1:B253"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>